--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.89233758143846</v>
+        <v>8.10750485698375</v>
       </c>
       <c r="D2" t="n">
-        <v>50.15154650385497</v>
+        <v>8.149626306876433</v>
       </c>
       <c r="E2" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F2" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.28032436336377</v>
+        <v>7.033052709046612</v>
       </c>
       <c r="D3" t="n">
-        <v>43.62045896063708</v>
+        <v>7.088324581103525</v>
       </c>
       <c r="E3" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F3" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.21845116621567</v>
+        <v>4.910498314510047</v>
       </c>
       <c r="D4" t="n">
-        <v>30.49116655349429</v>
+        <v>4.954814564942822</v>
       </c>
       <c r="E4" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F4" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.41699055513702</v>
+        <v>4.942760965209765</v>
       </c>
       <c r="D5" t="n">
-        <v>33.80901605101848</v>
+        <v>5.493965108290504</v>
       </c>
       <c r="E5" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F5" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.93629423052165</v>
+        <v>4.539647812459768</v>
       </c>
       <c r="D6" t="n">
-        <v>27.90998999144616</v>
+        <v>4.535373373610001</v>
       </c>
       <c r="E6" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F6" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.8062484748657</v>
+        <v>2.081015377165676</v>
       </c>
       <c r="D7" t="n">
-        <v>46.47590715021518</v>
+        <v>7.552334911909966</v>
       </c>
       <c r="E7" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F7" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.9413679053056</v>
+        <v>2.427972284612161</v>
       </c>
       <c r="D8" t="n">
-        <v>14.95292386959039</v>
+        <v>2.429850128808439</v>
       </c>
       <c r="E8" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F8" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.24907828052076</v>
+        <v>5.565475220584625</v>
       </c>
       <c r="D9" t="n">
-        <v>34.51212403388799</v>
+        <v>5.608220155506799</v>
       </c>
       <c r="E9" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F9" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>13.60147050873544</v>
+        <v>2.21023895766951</v>
       </c>
       <c r="D10" t="n">
-        <v>30.41704072733694</v>
+        <v>4.942769118192253</v>
       </c>
       <c r="E10" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F10" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.5837430301581</v>
+        <v>6.432358242400691</v>
       </c>
       <c r="D11" t="n">
-        <v>39.32495523493278</v>
+        <v>6.390305225676577</v>
       </c>
       <c r="E11" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F11" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.37201725495904</v>
+        <v>4.610452803930844</v>
       </c>
       <c r="D12" t="n">
-        <v>29.28514645733053</v>
+        <v>4.758836299316211</v>
       </c>
       <c r="E12" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F12" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>19.0105496926189</v>
+        <v>3.089214325050571</v>
       </c>
       <c r="D13" t="n">
-        <v>45.04161117814156</v>
+        <v>7.319261816448003</v>
       </c>
       <c r="E13" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F13" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>42.28908478320781</v>
+        <v>6.87197627727127</v>
       </c>
       <c r="D14" t="n">
-        <v>42.27451682048624</v>
+        <v>6.869608983329014</v>
       </c>
       <c r="E14" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F14" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>47.8976004200867</v>
+        <v>7.78336006826409</v>
       </c>
       <c r="D15" t="n">
-        <v>46.91420865536373</v>
+        <v>7.623558906496607</v>
       </c>
       <c r="E15" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F15" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>59.99669077021795</v>
+        <v>9.749462250160418</v>
       </c>
       <c r="D16" t="n">
-        <v>59.01679799844864</v>
+        <v>9.590229674747905</v>
       </c>
       <c r="E16" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F16" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>14.67309470402017</v>
+        <v>2.384377889403278</v>
       </c>
       <c r="D17" t="n">
-        <v>15.1020385767193</v>
+        <v>2.454081268716886</v>
       </c>
       <c r="E17" t="n">
-        <v>14.04027823439347</v>
+        <v>2.28154521308894</v>
       </c>
       <c r="F17" t="n">
-        <v>11.71769158775758</v>
+        <v>1.904124883010607</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
